--- a/assets/IDP_Employee_Input_Form.xlsx
+++ b/assets/IDP_Employee_Input_Form.xlsx
@@ -9,41 +9,86 @@
   </sheets>
   <definedNames>
     <definedName name="employee_name">'IDP Input Form'!$B$5</definedName>
-    <definedName name="manager_name">'IDP Input Form'!$F$5</definedName>
+    <definedName name="manager_name">'IDP Input Form'!$G$5</definedName>
     <definedName name="job_title">'IDP Input Form'!$B$6</definedName>
-    <definedName name="department">'IDP Input Form'!$F$6</definedName>
+    <definedName name="department">'IDP Input Form'!$G$6</definedName>
     <definedName name="plan_date">'IDP Input Form'!$B$9</definedName>
-    <definedName name="plan_year">'IDP Input Form'!$D$9</definedName>
-    <definedName name="status">'IDP Input Form'!$F$9</definedName>
+    <definedName name="plan_year">'IDP Input Form'!$E$9</definedName>
+    <definedName name="status">'IDP Input Form'!$G$9</definedName>
     <definedName name="milestone_count">'IDP Input Form'!$B$10</definedName>
-    <definedName name="plan_notes">'IDP Input Form'!$D$10</definedName>
+    <definedName name="plan_notes">'IDP Input Form'!$E$10</definedName>
     <definedName name="item1_description">'IDP Input Form'!$B$14</definedName>
     <definedName name="item1_due_date">'IDP Input Form'!$C$14</definedName>
-    <definedName name="item1_support_needed">'IDP Input Form'!$D$14</definedName>
+    <definedName name="item1_cost_estimate">'IDP Input Form'!$D$14</definedName>
+    <definedName name="item1_support_needed">'IDP Input Form'!$E$14</definedName>
     <definedName name="item2_description">'IDP Input Form'!$B$15</definedName>
     <definedName name="item2_due_date">'IDP Input Form'!$C$15</definedName>
-    <definedName name="item2_support_needed">'IDP Input Form'!$D$15</definedName>
+    <definedName name="item2_cost_estimate">'IDP Input Form'!$D$15</definedName>
+    <definedName name="item2_support_needed">'IDP Input Form'!$E$15</definedName>
     <definedName name="item3_description">'IDP Input Form'!$B$16</definedName>
     <definedName name="item3_due_date">'IDP Input Form'!$C$16</definedName>
-    <definedName name="item3_support_needed">'IDP Input Form'!$D$16</definedName>
+    <definedName name="item3_cost_estimate">'IDP Input Form'!$D$16</definedName>
+    <definedName name="item3_support_needed">'IDP Input Form'!$E$16</definedName>
     <definedName name="item4_description">'IDP Input Form'!$B$17</definedName>
     <definedName name="item4_due_date">'IDP Input Form'!$C$17</definedName>
-    <definedName name="item4_support_needed">'IDP Input Form'!$D$17</definedName>
+    <definedName name="item4_cost_estimate">'IDP Input Form'!$D$17</definedName>
+    <definedName name="item4_support_needed">'IDP Input Form'!$E$17</definedName>
     <definedName name="item5_description">'IDP Input Form'!$B$18</definedName>
     <definedName name="item5_due_date">'IDP Input Form'!$C$18</definedName>
-    <definedName name="item5_support_needed">'IDP Input Form'!$D$18</definedName>
+    <definedName name="item5_cost_estimate">'IDP Input Form'!$D$18</definedName>
+    <definedName name="item5_support_needed">'IDP Input Form'!$E$18</definedName>
+    <definedName name="item1_q1_status">'IDP Input Form'!$B$22</definedName>
+    <definedName name="item1_q1_notes">'IDP Input Form'!$C$22</definedName>
+    <definedName name="item1_q2_status">'IDP Input Form'!$D$22</definedName>
+    <definedName name="item1_q2_notes">'IDP Input Form'!$E$22</definedName>
+    <definedName name="item1_q3_status">'IDP Input Form'!$F$22</definedName>
+    <definedName name="item1_q3_notes">'IDP Input Form'!$G$22</definedName>
+    <definedName name="item1_q4_status">'IDP Input Form'!$H$22</definedName>
+    <definedName name="item1_q4_notes">'IDP Input Form'!$I$22</definedName>
+    <definedName name="item2_q1_status">'IDP Input Form'!$B$23</definedName>
+    <definedName name="item2_q1_notes">'IDP Input Form'!$C$23</definedName>
+    <definedName name="item2_q2_status">'IDP Input Form'!$D$23</definedName>
+    <definedName name="item2_q2_notes">'IDP Input Form'!$E$23</definedName>
+    <definedName name="item2_q3_status">'IDP Input Form'!$F$23</definedName>
+    <definedName name="item2_q3_notes">'IDP Input Form'!$G$23</definedName>
+    <definedName name="item2_q4_status">'IDP Input Form'!$H$23</definedName>
+    <definedName name="item2_q4_notes">'IDP Input Form'!$I$23</definedName>
+    <definedName name="item3_q1_status">'IDP Input Form'!$B$24</definedName>
+    <definedName name="item3_q1_notes">'IDP Input Form'!$C$24</definedName>
+    <definedName name="item3_q2_status">'IDP Input Form'!$D$24</definedName>
+    <definedName name="item3_q2_notes">'IDP Input Form'!$E$24</definedName>
+    <definedName name="item3_q3_status">'IDP Input Form'!$F$24</definedName>
+    <definedName name="item3_q3_notes">'IDP Input Form'!$G$24</definedName>
+    <definedName name="item3_q4_status">'IDP Input Form'!$H$24</definedName>
+    <definedName name="item3_q4_notes">'IDP Input Form'!$I$24</definedName>
+    <definedName name="item4_q1_status">'IDP Input Form'!$B$25</definedName>
+    <definedName name="item4_q1_notes">'IDP Input Form'!$C$25</definedName>
+    <definedName name="item4_q2_status">'IDP Input Form'!$D$25</definedName>
+    <definedName name="item4_q2_notes">'IDP Input Form'!$E$25</definedName>
+    <definedName name="item4_q3_status">'IDP Input Form'!$F$25</definedName>
+    <definedName name="item4_q3_notes">'IDP Input Form'!$G$25</definedName>
+    <definedName name="item4_q4_status">'IDP Input Form'!$H$25</definedName>
+    <definedName name="item4_q4_notes">'IDP Input Form'!$I$25</definedName>
+    <definedName name="item5_q1_status">'IDP Input Form'!$B$26</definedName>
+    <definedName name="item5_q1_notes">'IDP Input Form'!$C$26</definedName>
+    <definedName name="item5_q2_status">'IDP Input Form'!$D$26</definedName>
+    <definedName name="item5_q2_notes">'IDP Input Form'!$E$26</definedName>
+    <definedName name="item5_q3_status">'IDP Input Form'!$F$26</definedName>
+    <definedName name="item5_q3_notes">'IDP Input Form'!$G$26</definedName>
+    <definedName name="item5_q4_status">'IDP Input Form'!$H$26</definedName>
+    <definedName name="item5_q4_notes">'IDP Input Form'!$I$26</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="40">
-  <si>
-    <t>Paul Selby's IDP Tool — Employee Development Plan Input Form</t>
-  </si>
-  <si>
-    <t>Complete all required fields (*) and return this file to your manager for import into the IDP system.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="58">
+  <si>
+    <t>Employee Development Plan Input Form</t>
+  </si>
+  <si>
+    <t>Complete all required fields (*) and return this file to your manager.</t>
   </si>
   <si>
     <t>SECTION 1 — EMPLOYEE INFORMATION</t>
@@ -91,23 +136,68 @@
     <t>#</t>
   </si>
   <si>
-    <t>Development Goal / Activity (Description)</t>
+    <t>Development Goal / Activity (Description) *</t>
   </si>
   <si>
     <t xml:space="preserve">Due Date
 (YYYY-MM-DD)</t>
   </si>
   <si>
+    <t xml:space="preserve">Estimated
+Cost</t>
+  </si>
+  <si>
     <t>Support Needed</t>
   </si>
   <si>
+    <t>SECTION 4 — QUARTERLY MILESTONE CHECK-INS  (fill in your progress for each item per period)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item
+#</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q1 / Period 1
+Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q1 / Period 1
+Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q2 / Period 2
+Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q2 / Period 2
+Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q3 / Period 3
+Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q3 / Period 3
+Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q4 / Period 4
+Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q4 / Period 4
+Notes</t>
+  </si>
+  <si>
+    <t>Not Started</t>
+  </si>
+  <si>
     <t>HOW TO SUBMIT THIS FORM</t>
   </si>
   <si>
     <t xml:space="preserve">1. Fill in all fields marked with * (required).
-2. Add your development goals in Section 3 — you only need to fill in rows you are using.
-3. Save this file and email it (or share via Teams/SharePoint) to your manager.
-4. Your manager will import it into the IDP Tool using File → Import Employee Form.</t>
+2. Add your development goals in Section 3 — fill in only the rows you are using.
+3. Save this file and email it (or share via Teams/SharePoint) to your manager.</t>
   </si>
   <si>
     <t>IDP Input Form — Field Reference Guide</t>
@@ -165,14 +255,32 @@
     <t>Target completion date for this specific item (YYYY-MM-DD).</t>
   </si>
   <si>
+    <t>Estimated Cost</t>
+  </si>
+  <si>
+    <t>Estimated cost for this item, e.g., "$500" or "1200". Free text — no specific format required. Leave blank if none.</t>
+  </si>
+  <si>
     <t>Resources required: training budget, exam fee, manager coaching, etc.</t>
+  </si>
+  <si>
+    <t>Q1–Q4 Status</t>
+  </si>
+  <si>
+    <t>Your progress in that period: Not Started, In Progress, or Complete.</t>
+  </si>
+  <si>
+    <t>Q1–Q4 Notes</t>
+  </si>
+  <si>
+    <t>Brief notes on what you did or plan to do in that period (optional).</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -214,6 +322,12 @@
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="8"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -324,7 +438,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -355,22 +469,25 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -715,17 +832,20 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" defaultColWidth="20"/>
+  <dimension ref="A1:I31"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" defaultColWidth="18"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="6" width="22" customWidth="1"/>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="28" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="28" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -734,8 +854,11 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
-    </row>
-    <row r="2" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -744,9 +867,12 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
     </row>
     <row r="3" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -755,33 +881,42 @@
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
-    </row>
-    <row r="5" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+    </row>
+    <row r="5" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5"/>
+      <c r="F5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="5"/>
-    </row>
-    <row r="6" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+    </row>
+    <row r="6" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5"/>
+      <c r="F6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
     </row>
     <row r="7" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
@@ -790,41 +925,50 @@
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
-    </row>
-    <row r="9" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="5"/>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5"/>
+      <c r="D9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="7">
+      <c r="E9" s="7">
         <v>2026</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="F9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="G9" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="10" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+    </row>
+    <row r="10" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="5"/>
+      <c r="D10" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="5"/>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
     </row>
     <row r="11" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>15</v>
       </c>
@@ -833,8 +977,11 @@
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
-    </row>
-    <row r="13" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+    </row>
+    <row r="13" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>16</v>
       </c>
@@ -847,10 +994,15 @@
       <c r="D13" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="8"/>
+      <c r="E13" s="8" t="s">
+        <v>20</v>
+      </c>
       <c r="F13" s="8"/>
-    </row>
-    <row r="14" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+    </row>
+    <row r="14" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
         <v>1</v>
       </c>
@@ -859,8 +1011,11 @@
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
-    </row>
-    <row r="15" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+    </row>
+    <row r="15" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
         <v>2</v>
       </c>
@@ -869,8 +1024,11 @@
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
-    </row>
-    <row r="16" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+    </row>
+    <row r="16" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
         <v>3</v>
       </c>
@@ -879,8 +1037,11 @@
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
-    </row>
-    <row r="17" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+    </row>
+    <row r="17" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
         <v>4</v>
       </c>
@@ -889,8 +1050,11 @@
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
-    </row>
-    <row r="18" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+    </row>
+    <row r="18" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
         <v>5</v>
       </c>
@@ -899,202 +1063,399 @@
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
     </row>
     <row r="19" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-    </row>
-    <row r="21" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
+    <row r="20" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-    </row>
-    <row r="22" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="11"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-    </row>
-    <row r="23" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="11"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-    </row>
-    <row r="24" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="11"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+    </row>
+    <row r="21" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="9">
+        <v>1</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I22" s="5"/>
+    </row>
+    <row r="23" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="9">
+        <v>2</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I23" s="5"/>
+    </row>
+    <row r="24" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="9">
+        <v>3</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I24" s="5"/>
+    </row>
+    <row r="25" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="9">
+        <v>4</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" s="5"/>
+    </row>
+    <row r="26" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="9">
+        <v>5</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I26" s="5"/>
+    </row>
+    <row r="27" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="16" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+    </row>
+    <row r="29" ht="14" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+    </row>
+    <row r="30" ht="14" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="12"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+    </row>
+    <row r="31" ht="14" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="12"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1"/>
-  <mergeCells count="16">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A21:F24"/>
+  <mergeCells count="22">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="E10:I10"/>
+    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="E13:I13"/>
+    <mergeCell ref="E14:I14"/>
+    <mergeCell ref="E15:I15"/>
+    <mergeCell ref="E16:I16"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="E18:I18"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="A29:I31"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="6">
     <dataValidation type="list" showErrorMessage="1" errorTitle="Invalid Selection" error="Please select a milestone period from the dropdown list." sqref="B10">
       <formula1>"2 — Semi-Annual (H1–H2),3 — Thirds (T1–T3),4 — Quarterly (Q1–Q4),6 — Bi-Monthly (B1–B6),12 — Monthly (M1–M12)"</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" errorTitle="Invalid Status" error="Please select: Active, Inactive, or Complete" sqref="F9">
+    <dataValidation type="list" showErrorMessage="1" errorTitle="Invalid Status" error="Please select: Not Started, In Progress, or Complete" sqref="B22:B26">
+      <formula1>"Not Started,In Progress,Complete"</formula1>
+    </dataValidation>
+    <dataValidation type="list" showErrorMessage="1" errorTitle="Invalid Status" error="Please select: Not Started, In Progress, or Complete" sqref="D22:D26">
+      <formula1>"Not Started,In Progress,Complete"</formula1>
+    </dataValidation>
+    <dataValidation type="list" showErrorMessage="1" errorTitle="Invalid Status" error="Please select: Not Started, In Progress, or Complete" sqref="F22:F26">
+      <formula1>"Not Started,In Progress,Complete"</formula1>
+    </dataValidation>
+    <dataValidation type="list" showErrorMessage="1" errorTitle="Invalid Status" error="Please select: Active, Inactive, or Complete" sqref="G9">
       <formula1>"Active,Inactive,Complete"</formula1>
+    </dataValidation>
+    <dataValidation type="list" showErrorMessage="1" errorTitle="Invalid Status" error="Please select: Not Started, In Progress, or Complete" sqref="H22:H26">
+      <formula1>"Not Started,In Progress,Complete"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" defaultColWidth="30"/>
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="60" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="65" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" s="12"/>
+      <c r="A1" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="13"/>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>24</v>
+      <c r="A2" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="15" t="s">
-        <v>25</v>
+      <c r="B3" s="16" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="15" t="s">
-        <v>26</v>
+      <c r="B4" s="16" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="15" t="s">
-        <v>27</v>
+      <c r="B5" s="16" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="15" t="s">
-        <v>28</v>
+      <c r="B6" s="16" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>30</v>
+      <c r="A7" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="15" t="s">
-        <v>31</v>
+      <c r="B8" s="16" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="15" t="s">
-        <v>32</v>
+      <c r="B9" s="16" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="10" ht="80" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="15" t="s">
-        <v>33</v>
+      <c r="B10" s="16" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="15" t="s">
-        <v>34</v>
+      <c r="B11" s="16" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>36</v>
+      <c r="A12" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>38</v>
+      <c r="A13" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>39</v>
+      <c r="A14" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
